--- a/CPRD Raw Analysis/Results/Output_yearly_costs_Raw-Boot.xlsx
+++ b/CPRD Raw Analysis/Results/Output_yearly_costs_Raw-Boot.xlsx
@@ -384,13 +384,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>629.808</v>
+        <v>532.652</v>
       </c>
       <c r="C2">
-        <v>622.827</v>
+        <v>524.9829999999999</v>
       </c>
       <c r="D2">
-        <v>636.857</v>
+        <v>540.655</v>
       </c>
     </row>
     <row r="3">
@@ -398,13 +398,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>442.324</v>
+        <v>361.508</v>
       </c>
       <c r="C3">
-        <v>435.852</v>
+        <v>354.582</v>
       </c>
       <c r="D3">
-        <v>448.668</v>
+        <v>368.22</v>
       </c>
     </row>
   </sheetData>
@@ -444,13 +444,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>639.737</v>
+        <v>547.569</v>
       </c>
       <c r="C2">
-        <v>633.008</v>
+        <v>539.961</v>
       </c>
       <c r="D2">
-        <v>646.7569999999999</v>
+        <v>555.307</v>
       </c>
     </row>
     <row r="3">
@@ -458,13 +458,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>449.298</v>
+        <v>371.632</v>
       </c>
       <c r="C3">
-        <v>443.165</v>
+        <v>364.378</v>
       </c>
       <c r="D3">
-        <v>455.633</v>
+        <v>378.775</v>
       </c>
     </row>
   </sheetData>
@@ -504,13 +504,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>662.463</v>
+        <v>624.89</v>
       </c>
       <c r="C2">
-        <v>654.979</v>
+        <v>616.074</v>
       </c>
       <c r="D2">
-        <v>669.516</v>
+        <v>633.722</v>
       </c>
     </row>
     <row r="3">
@@ -518,13 +518,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>469.079</v>
+        <v>443.499</v>
       </c>
       <c r="C3">
-        <v>462.358</v>
+        <v>435.143</v>
       </c>
       <c r="D3">
-        <v>475.339</v>
+        <v>451.644</v>
       </c>
     </row>
   </sheetData>
@@ -564,13 +564,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>669.9299999999999</v>
+        <v>633.679</v>
       </c>
       <c r="C2">
-        <v>662.514</v>
+        <v>624.8339999999999</v>
       </c>
       <c r="D2">
-        <v>677.275</v>
+        <v>642.943</v>
       </c>
     </row>
     <row r="3">
@@ -578,13 +578,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>474.366</v>
+        <v>449.736</v>
       </c>
       <c r="C3">
-        <v>467.836</v>
+        <v>441.725</v>
       </c>
       <c r="D3">
-        <v>481.202</v>
+        <v>457.904</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/Output_yearly_costs_Raw-Boot.xlsx
+++ b/CPRD Raw Analysis/Results/Output_yearly_costs_Raw-Boot.xlsx
@@ -384,13 +384,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>532.652</v>
+        <v>493.758</v>
       </c>
       <c r="C2">
-        <v>524.9829999999999</v>
+        <v>486.255</v>
       </c>
       <c r="D2">
-        <v>540.655</v>
+        <v>501.628</v>
       </c>
     </row>
     <row r="3">
@@ -398,13 +398,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>361.508</v>
+        <v>267.947</v>
       </c>
       <c r="C3">
-        <v>354.582</v>
+        <v>261.301</v>
       </c>
       <c r="D3">
-        <v>368.22</v>
+        <v>274.316</v>
       </c>
     </row>
   </sheetData>
@@ -444,13 +444,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>547.569</v>
+        <v>517.204</v>
       </c>
       <c r="C2">
-        <v>539.961</v>
+        <v>509.769</v>
       </c>
       <c r="D2">
-        <v>555.307</v>
+        <v>524.8099999999999</v>
       </c>
     </row>
     <row r="3">
@@ -458,13 +458,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>371.632</v>
+        <v>280.671</v>
       </c>
       <c r="C3">
-        <v>364.378</v>
+        <v>274.024</v>
       </c>
       <c r="D3">
-        <v>378.775</v>
+        <v>287.437</v>
       </c>
     </row>
   </sheetData>
@@ -504,13 +504,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>624.89</v>
+        <v>477.522</v>
       </c>
       <c r="C2">
-        <v>616.074</v>
+        <v>469.718</v>
       </c>
       <c r="D2">
-        <v>633.722</v>
+        <v>485.455</v>
       </c>
     </row>
     <row r="3">
@@ -518,13 +518,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>443.499</v>
+        <v>272.525</v>
       </c>
       <c r="C3">
-        <v>435.143</v>
+        <v>266.026</v>
       </c>
       <c r="D3">
-        <v>451.644</v>
+        <v>278.887</v>
       </c>
     </row>
   </sheetData>
@@ -564,13 +564,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>633.679</v>
+        <v>831.283</v>
       </c>
       <c r="C2">
-        <v>624.8339999999999</v>
+        <v>816.047</v>
       </c>
       <c r="D2">
-        <v>642.943</v>
+        <v>847.384</v>
       </c>
     </row>
     <row r="3">
@@ -578,13 +578,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>449.736</v>
+        <v>472.464</v>
       </c>
       <c r="C3">
-        <v>441.725</v>
+        <v>459.883</v>
       </c>
       <c r="D3">
-        <v>457.904</v>
+        <v>485.222</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/Output_yearly_costs_Raw-Boot.xlsx
+++ b/CPRD Raw Analysis/Results/Output_yearly_costs_Raw-Boot.xlsx
@@ -384,13 +384,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>493.758</v>
+        <v>545.188</v>
       </c>
       <c r="C2">
-        <v>486.255</v>
+        <v>538.802</v>
       </c>
       <c r="D2">
-        <v>501.628</v>
+        <v>551.818</v>
       </c>
     </row>
     <row r="3">
@@ -398,13 +398,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>267.947</v>
+        <v>287.711</v>
       </c>
       <c r="C3">
-        <v>261.301</v>
+        <v>282.029</v>
       </c>
       <c r="D3">
-        <v>274.316</v>
+        <v>293.622</v>
       </c>
     </row>
   </sheetData>
@@ -444,13 +444,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>517.204</v>
+        <v>562.1950000000001</v>
       </c>
       <c r="C2">
-        <v>509.769</v>
+        <v>555.174</v>
       </c>
       <c r="D2">
-        <v>524.8099999999999</v>
+        <v>568.841</v>
       </c>
     </row>
     <row r="3">
@@ -458,13 +458,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>280.671</v>
+        <v>296.686</v>
       </c>
       <c r="C3">
-        <v>274.024</v>
+        <v>290.885</v>
       </c>
       <c r="D3">
-        <v>287.437</v>
+        <v>302.479</v>
       </c>
     </row>
   </sheetData>
@@ -504,13 +504,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>477.522</v>
+        <v>523.138</v>
       </c>
       <c r="C2">
-        <v>469.718</v>
+        <v>515.548</v>
       </c>
       <c r="D2">
-        <v>485.455</v>
+        <v>530.431</v>
       </c>
     </row>
     <row r="3">
@@ -518,13 +518,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>272.525</v>
+        <v>290.83</v>
       </c>
       <c r="C3">
-        <v>266.026</v>
+        <v>284.751</v>
       </c>
       <c r="D3">
-        <v>278.887</v>
+        <v>297.066</v>
       </c>
     </row>
   </sheetData>
@@ -564,13 +564,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>831.283</v>
+        <v>926.919</v>
       </c>
       <c r="C2">
-        <v>816.047</v>
+        <v>912.236</v>
       </c>
       <c r="D2">
-        <v>847.384</v>
+        <v>941.251</v>
       </c>
     </row>
     <row r="3">
@@ -578,13 +578,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>472.464</v>
+        <v>511.979</v>
       </c>
       <c r="C3">
-        <v>459.883</v>
+        <v>500.367</v>
       </c>
       <c r="D3">
-        <v>485.222</v>
+        <v>523.785</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/Output_yearly_costs_Raw-Boot.xlsx
+++ b/CPRD Raw Analysis/Results/Output_yearly_costs_Raw-Boot.xlsx
@@ -384,13 +384,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>545.188</v>
+        <v>721.818</v>
       </c>
       <c r="C2">
-        <v>538.802</v>
+        <v>712.2670000000001</v>
       </c>
       <c r="D2">
-        <v>551.818</v>
+        <v>731.1319999999999</v>
       </c>
     </row>
     <row r="3">
@@ -398,13 +398,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>287.711</v>
+        <v>383.917</v>
       </c>
       <c r="C3">
-        <v>282.029</v>
+        <v>375.921</v>
       </c>
       <c r="D3">
-        <v>293.622</v>
+        <v>391.951</v>
       </c>
     </row>
   </sheetData>
@@ -444,13 +444,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>562.1950000000001</v>
+        <v>717.254</v>
       </c>
       <c r="C2">
-        <v>555.174</v>
+        <v>707.449</v>
       </c>
       <c r="D2">
-        <v>568.841</v>
+        <v>726.7089999999999</v>
       </c>
     </row>
     <row r="3">
@@ -458,13 +458,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>296.686</v>
+        <v>384.019</v>
       </c>
       <c r="C3">
-        <v>290.885</v>
+        <v>376.079</v>
       </c>
       <c r="D3">
-        <v>302.479</v>
+        <v>391.871</v>
       </c>
     </row>
   </sheetData>
@@ -504,13 +504,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>523.138</v>
+        <v>863.52</v>
       </c>
       <c r="C2">
-        <v>515.548</v>
+        <v>851.9450000000001</v>
       </c>
       <c r="D2">
-        <v>530.431</v>
+        <v>875.117</v>
       </c>
     </row>
     <row r="3">
@@ -518,13 +518,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>290.83</v>
+        <v>483.004</v>
       </c>
       <c r="C3">
-        <v>284.751</v>
+        <v>473.282</v>
       </c>
       <c r="D3">
-        <v>297.066</v>
+        <v>493.134</v>
       </c>
     </row>
   </sheetData>
@@ -564,13 +564,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>926.919</v>
+        <v>1197.077</v>
       </c>
       <c r="C2">
-        <v>912.236</v>
+        <v>1178.011</v>
       </c>
       <c r="D2">
-        <v>941.251</v>
+        <v>1215.897</v>
       </c>
     </row>
     <row r="3">
@@ -578,13 +578,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>511.979</v>
+        <v>668.353</v>
       </c>
       <c r="C3">
-        <v>500.367</v>
+        <v>651.909</v>
       </c>
       <c r="D3">
-        <v>523.785</v>
+        <v>684.136</v>
       </c>
     </row>
   </sheetData>
